--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Residenza.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Residenza.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
   <si>
     <r>
       <t xml:space="preserve">
@@ -74,21 +74,6 @@
   </si>
   <si>
     <t>Messaggi presenti in questo template</t>
-  </si>
-  <si>
-    <t>Richiesta di residenza, cambio, cancellazione: avviamento del procedimento</t>
-  </si>
-  <si>
-    <t>Richiesta di residenza, cambio, cancellazione: integrazione documentazione</t>
-  </si>
-  <si>
-    <t>Avvenuto cambio di residenza (da altro comune o dall’estero)</t>
-  </si>
-  <si>
-    <t>Avvenuta cancellazione di residenza</t>
-  </si>
-  <si>
-    <t>Richiesta di residenza, cambio, cancellazione: non accolta</t>
   </si>
   <si>
     <t>Richiesta di residenza temporanea: accolta</t>
@@ -274,90 +259,6 @@
     <r>
       <rPr>
         <b/>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;Cambio/Cancellazione/Richiesta&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> di residenza in corso</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Richiesta di integrazione</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Avvenuto cambio di residenza</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Avvenuta cancellazione di residenza</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">Richiesta di </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;cambio/cancellazione/residenza&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> non accolta</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <family val="2"/>
         <sz val="10"/>
         <rFont val="Titillium Web"/>
@@ -387,234 +288,6 @@
       <rPr/>
       <t xml:space="preserve">
 Testo definitivo da inviare al cittadino. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">Abbiamo avviato il procedimento per la tua richiesta di </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;cambio/cancellazione/residenza&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Il numero di pratica è:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;nnnn&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">Per elaborare la tua </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;richiesta di cambio/richiesta di cancellazione/richiesta&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> di residenza, abbiamo bisogno di ricevere entro il </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;gg/mm/aaaa&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> altri documenti.
-Consulta il riepilogo della tua richiesta, [visita questo sito](URL).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">Ti diamo il benvenuto nel Comune di </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;Comune&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">.
-Nei prossimi </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;nn&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> giorni un messo comunale o un agente della Polizia locale verrà presso la tua abitazione per l’accertamento della residenza.
-Se non lo hai già fatto, aggiorna la tua dichiarazione TARI (Tassa sui Rifiuti). Per farlo, [visita questo sito](URL).
-Per ulteriori informazioni, [visita questo sito](URL).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">Il </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;gg/mm/aaaa&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> abbiamo provveduto a cancellare la tua residenza presso il Comune di </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;Comune&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">.
-Se non lo hai già fatto, aggiorna la tua dichiarazione TARI (Tassa sui Rifiuti). Per aggiornare la dichiarazione TARI [visita questo sito](URL).
-Per ulteriori informazioni, [visita questo sito](URL).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">La tua </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;richiesta di cambio/richiesta di cancellazione/richiesta&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> di residenza non è stata accolta.
-Per ulteriori informazioni, [visita questa pagina](URL).</t>
     </r>
   </si>
   <si>
@@ -670,12 +343,6 @@
     </r>
   </si>
   <si>
-    <t>Gestisci la tua richiesta</t>
-  </si>
-  <si>
-    <t>Aggiungi documenti</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -696,7 +363,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -718,15 +385,6 @@
     </r>
   </si>
   <si>
-    <t>Tutte le persone che hanno presentato richiesta, cambio o cancellazione di residenza.</t>
-  </si>
-  <si>
-    <t>Tutte le persone che hanno presentato richiesta e cambio di residenza.</t>
-  </si>
-  <si>
-    <t>Tutte le persone che hanno presentato richiesta di cancellazione residenza.</t>
-  </si>
-  <si>
     <t>Tutte le persone che hanno presentato richiesta di iscrizione al registro dell’anagrafe temporanea.</t>
   </si>
   <si>
@@ -743,19 +401,10 @@
     </r>
   </si>
   <si>
-    <t>Quando l’ente prende in carico la pratica e avvia il procedimento.</t>
-  </si>
-  <si>
-    <t>Quando l’ente ha bisogno di ulteriori documenti per l’elaborazione della richiesta.</t>
-  </si>
-  <si>
-    <t>Quando l’ente effettua l’iscrizione anagrafica.</t>
+    <t>Quando l’ente comunica l’iscrizione al registro dell’anagrafe temporanea.</t>
   </si>
   <si>
     <t>Quando l’ente identifica ragioni ostative al completamento della richiesta.</t>
-  </si>
-  <si>
-    <t>Quando l’ente comunica l’iscrizione al registro dell’anagrafe temporanea.</t>
   </si>
   <si>
     <r>
@@ -1325,16 +974,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="8" width="35" customWidth="1"/>
+    <col min="2" max="3" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>9</v>
@@ -1342,280 +991,115 @@
       <c r="C1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="33" t="s">
-        <v>11</v>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
+        <v>53</v>
       </c>
-      <c r="E1" s="33" t="s">
-        <v>12</v>
+      <c r="B2" s="34" t="s">
+        <v>54</v>
       </c>
-      <c r="F1" s="33" t="s">
-        <v>13</v>
+      <c r="C2" s="34" t="s">
+        <v>54</v>
       </c>
-      <c r="G1" s="33" t="s">
-        <v>14</v>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>55</v>
       </c>
-      <c r="H1" s="33" t="s">
-        <v>15</v>
+      <c r="B3" s="34" t="s">
+        <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="C3" s="34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="C4" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" s="34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B5" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="C5" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="33" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="B6" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="C6" s="34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="B7" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="B8" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="B9" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="C9" s="34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="B10" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="C10" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="34" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>95</v>
-      </c>
       <c r="B11" s="34" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1642,7 +1126,7 @@
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="13" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -1672,10 +1156,10 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
@@ -1705,10 +1189,10 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1738,10 +1222,10 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
@@ -1771,10 +1255,10 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -1804,13 +1288,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="22"/>
@@ -1839,10 +1323,10 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -1872,13 +1356,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
@@ -1907,13 +1391,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26"/>
@@ -1942,10 +1426,10 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
@@ -1975,10 +1459,10 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
@@ -2008,10 +1492,10 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
@@ -2041,10 +1525,10 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
@@ -2074,10 +1558,10 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
@@ -2107,10 +1591,10 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -2140,10 +1624,10 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
@@ -2173,10 +1657,10 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -2206,10 +1690,10 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C18" s="29"/>
       <c r="D18" s="29"/>
@@ -2239,10 +1723,10 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C19" s="22"/>
       <c r="D19" s="22"/>
@@ -2272,7 +1756,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="30"/>
@@ -30730,33 +30214,23 @@
     </row>
     <row r="15" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
-      <c r="B15" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="B15" s="10"/>
     </row>
     <row r="16" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
-      <c r="B16" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="B16" s="10"/>
     </row>
     <row r="17" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
-      <c r="B17" s="11" t="s">
-        <v>13</v>
-      </c>
+      <c r="B17" s="10"/>
     </row>
     <row r="18" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
-      <c r="B18" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="B18" s="10"/>
     </row>
     <row r="19" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
-      <c r="B19" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="B19" s="10"/>
     </row>
     <row r="20" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
@@ -30959,13 +30433,8 @@
     <hyperlink ref="B9" r:id="rId1"/>
     <hyperlink ref="B13" r:id="rId2" tooltip="Vai al template del messaggio" location="#'Template messaggi'!B1"/>
     <hyperlink ref="B14" r:id="rId3" tooltip="Vai al template del messaggio" location="#'Template messaggi'!C1"/>
-    <hyperlink ref="B15" r:id="rId4" tooltip="Vai al template del messaggio" location="#'Template messaggi'!D1"/>
-    <hyperlink ref="B16" r:id="rId5" tooltip="Vai al template del messaggio" location="#'Template messaggi'!E1"/>
-    <hyperlink ref="B17" r:id="rId6" tooltip="Vai al template del messaggio" location="#'Template messaggi'!F1"/>
-    <hyperlink ref="B18" r:id="rId7" tooltip="Vai al template del messaggio" location="#'Template messaggi'!G1"/>
-    <hyperlink ref="B19" r:id="rId8" tooltip="Vai al template del messaggio" location="#'Template messaggi'!H1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId9"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>